--- a/data/nzd0535/nzd0535.xlsx
+++ b/data/nzd0535/nzd0535.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N478"/>
+  <dimension ref="A1:N479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23392,6 +23392,54 @@
       <c r="N478" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>325.51</v>
+      </c>
+      <c r="C479" t="n">
+        <v>317.51</v>
+      </c>
+      <c r="D479" t="n">
+        <v>319.89</v>
+      </c>
+      <c r="E479" t="n">
+        <v>319.63</v>
+      </c>
+      <c r="F479" t="n">
+        <v>322.53</v>
+      </c>
+      <c r="G479" t="n">
+        <v>322.28</v>
+      </c>
+      <c r="H479" t="n">
+        <v>318.43</v>
+      </c>
+      <c r="I479" t="n">
+        <v>321.22</v>
+      </c>
+      <c r="J479" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="K479" t="n">
+        <v>319.73</v>
+      </c>
+      <c r="L479" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="M479" t="n">
+        <v>312.04</v>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23406,7 +23454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B534"/>
+  <dimension ref="A1:B535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28749,6 +28797,16 @@
       </c>
       <c r="B534" t="n">
         <v>0.45</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -28917,28 +28975,28 @@
         <v>0.1816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1767077436601391</v>
+        <v>0.175588834140402</v>
       </c>
       <c r="J2" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K2" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06293649752652208</v>
+        <v>0.06242088391731648</v>
       </c>
       <c r="M2" t="n">
-        <v>3.671559614760795</v>
+        <v>3.668825535217538</v>
       </c>
       <c r="N2" t="n">
-        <v>26.272495700907</v>
+        <v>26.23317271085456</v>
       </c>
       <c r="O2" t="n">
-        <v>5.125670268453385</v>
+        <v>5.121832944450118</v>
       </c>
       <c r="P2" t="n">
-        <v>323.5988377730314</v>
+        <v>323.6102450531363</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28995,28 +29053,28 @@
         <v>0.127</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3293708818268024</v>
+        <v>0.328658252451489</v>
       </c>
       <c r="J3" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K3" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2283941431097654</v>
+        <v>0.2283739379953386</v>
       </c>
       <c r="M3" t="n">
-        <v>3.284619853811748</v>
+        <v>3.281488287736198</v>
       </c>
       <c r="N3" t="n">
-        <v>20.71117183319188</v>
+        <v>20.6741873418732</v>
       </c>
       <c r="O3" t="n">
-        <v>4.550952848930856</v>
+        <v>4.546887654415182</v>
       </c>
       <c r="P3" t="n">
-        <v>310.5712734086983</v>
+        <v>310.57853866362</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29073,28 +29131,28 @@
         <v>0.0954</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2345420740698561</v>
+        <v>0.2350342869200435</v>
       </c>
       <c r="J4" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K4" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1719242936062026</v>
+        <v>0.1731398518651897</v>
       </c>
       <c r="M4" t="n">
-        <v>2.899512563145724</v>
+        <v>2.895876051428078</v>
       </c>
       <c r="N4" t="n">
-        <v>14.97262790700299</v>
+        <v>14.944331076965</v>
       </c>
       <c r="O4" t="n">
-        <v>3.869448010634462</v>
+        <v>3.865789838695969</v>
       </c>
       <c r="P4" t="n">
-        <v>312.4977447937615</v>
+        <v>312.492726684831</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29151,28 +29209,28 @@
         <v>0.1367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2515106364274518</v>
+        <v>0.2520561914789583</v>
       </c>
       <c r="J5" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K5" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1792106665422569</v>
+        <v>0.1804836259967494</v>
       </c>
       <c r="M5" t="n">
-        <v>2.902103664512422</v>
+        <v>2.898977378898013</v>
       </c>
       <c r="N5" t="n">
-        <v>16.37209572393621</v>
+        <v>16.3415626952788</v>
       </c>
       <c r="O5" t="n">
-        <v>4.046244644597779</v>
+        <v>4.042469875617974</v>
       </c>
       <c r="P5" t="n">
-        <v>311.662753002725</v>
+        <v>311.6571910701689</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29229,28 +29287,28 @@
         <v>0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1914321497830193</v>
+        <v>0.1926226742268843</v>
       </c>
       <c r="J6" t="n">
+        <v>478</v>
+      </c>
+      <c r="K6" t="n">
         <v>477</v>
       </c>
-      <c r="K6" t="n">
-        <v>476</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1600589289249901</v>
+        <v>0.162124927866009</v>
       </c>
       <c r="M6" t="n">
-        <v>2.499299962787826</v>
+        <v>2.499637190878577</v>
       </c>
       <c r="N6" t="n">
-        <v>10.88759825831784</v>
+        <v>10.88252541065684</v>
       </c>
       <c r="O6" t="n">
-        <v>3.299636079678764</v>
+        <v>3.298867292065087</v>
       </c>
       <c r="P6" t="n">
-        <v>314.5586666770526</v>
+        <v>314.5465372528136</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29307,28 +29365,28 @@
         <v>0.1233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1322204665389149</v>
+        <v>0.132828008814176</v>
       </c>
       <c r="J7" t="n">
+        <v>478</v>
+      </c>
+      <c r="K7" t="n">
         <v>477</v>
       </c>
-      <c r="K7" t="n">
-        <v>476</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.09784174311035154</v>
+        <v>0.09901150209097065</v>
       </c>
       <c r="M7" t="n">
-        <v>2.29010031857576</v>
+        <v>2.288322346171951</v>
       </c>
       <c r="N7" t="n">
-        <v>9.126186519344662</v>
+        <v>9.111677130054515</v>
       </c>
       <c r="O7" t="n">
-        <v>3.020957881094118</v>
+        <v>3.018555470759899</v>
       </c>
       <c r="P7" t="n">
-        <v>317.30184335056</v>
+        <v>317.2956535255313</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29385,28 +29443,28 @@
         <v>0.106</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0001492637781317028</v>
+        <v>-0.0002443630857558775</v>
       </c>
       <c r="J8" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K8" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1592580484443e-07</v>
+        <v>3.12106396616052e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>2.557770871292214</v>
+        <v>2.552960057804724</v>
       </c>
       <c r="N8" t="n">
-        <v>10.86056462897572</v>
+        <v>10.83795676527657</v>
       </c>
       <c r="O8" t="n">
-        <v>3.295537077469425</v>
+        <v>3.292105217831983</v>
       </c>
       <c r="P8" t="n">
-        <v>318.6670975665239</v>
+        <v>318.668067103757</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29463,28 +29521,28 @@
         <v>0.1023</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07879569629304362</v>
+        <v>-0.07814959939141534</v>
       </c>
       <c r="J9" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K9" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03235050211834256</v>
+        <v>0.03196332071448504</v>
       </c>
       <c r="M9" t="n">
-        <v>2.639456561519852</v>
+        <v>2.637454094508729</v>
       </c>
       <c r="N9" t="n">
-        <v>10.49459683056129</v>
+        <v>10.47785659081397</v>
       </c>
       <c r="O9" t="n">
-        <v>3.239536514775114</v>
+        <v>3.236951743664704</v>
       </c>
       <c r="P9" t="n">
-        <v>321.716622130477</v>
+        <v>321.7100351739789</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29541,28 +29599,28 @@
         <v>0.1526</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08386230489087779</v>
+        <v>-0.08413000209255597</v>
       </c>
       <c r="J10" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K10" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0283765679618927</v>
+        <v>0.02867675915911505</v>
       </c>
       <c r="M10" t="n">
-        <v>2.868398962257087</v>
+        <v>2.863714003560974</v>
       </c>
       <c r="N10" t="n">
-        <v>13.60803491309141</v>
+        <v>13.5804614728158</v>
       </c>
       <c r="O10" t="n">
-        <v>3.688907007921371</v>
+        <v>3.685167767255081</v>
       </c>
       <c r="P10" t="n">
-        <v>324.4406337488942</v>
+        <v>324.4433629212795</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29619,28 +29677,28 @@
         <v>0.1109</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1408036161576538</v>
+        <v>-0.1410448045519885</v>
       </c>
       <c r="J11" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K11" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0853160117905335</v>
+        <v>0.08593346752310416</v>
       </c>
       <c r="M11" t="n">
-        <v>2.76952730167412</v>
+        <v>2.764882727883734</v>
       </c>
       <c r="N11" t="n">
-        <v>12.01135111459918</v>
+        <v>11.98694949058036</v>
       </c>
       <c r="O11" t="n">
-        <v>3.465739620138706</v>
+        <v>3.462217423932292</v>
       </c>
       <c r="P11" t="n">
-        <v>324.0380824329925</v>
+        <v>324.0405413481449</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29697,28 +29755,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1861168655899862</v>
+        <v>-0.1862972139444906</v>
       </c>
       <c r="J12" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K12" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1014145252967938</v>
+        <v>0.102002703494765</v>
       </c>
       <c r="M12" t="n">
-        <v>3.334422900533133</v>
+        <v>3.328429119634078</v>
       </c>
       <c r="N12" t="n">
-        <v>17.3442053128281</v>
+        <v>17.30832669739655</v>
       </c>
       <c r="O12" t="n">
-        <v>4.164637476759304</v>
+        <v>4.160327715144151</v>
       </c>
       <c r="P12" t="n">
-        <v>315.8547472541226</v>
+        <v>315.8565859052021</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29775,28 +29833,28 @@
         <v>0.0591</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2005131378982138</v>
+        <v>-0.2011146148138494</v>
       </c>
       <c r="J13" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K13" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1072431818280069</v>
+        <v>0.1082309218340276</v>
       </c>
       <c r="M13" t="n">
-        <v>3.412720292949477</v>
+        <v>3.408591112192336</v>
       </c>
       <c r="N13" t="n">
-        <v>18.91354190190378</v>
+        <v>18.87849337651534</v>
       </c>
       <c r="O13" t="n">
-        <v>4.348970211659742</v>
+        <v>4.344938823103881</v>
       </c>
       <c r="P13" t="n">
-        <v>318.8054988707809</v>
+        <v>318.8116309266194</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29834,7 +29892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N478"/>
+  <dimension ref="A1:N479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64245,6 +64303,78 @@
         </is>
       </c>
     </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>-46.38424073846623,168.0290251048334</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>-46.38402300954265,168.02818233571188</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>-46.383894748280824,168.0273015824391</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-46.38374373177539,168.02643049002498</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>-46.38361995151409,168.02554783317856</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>-46.38346902033839,168.02467670399824</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>-46.38328705986208,168.02381875014945</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>-46.383162330101364,168.02293649529352</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>-46.383014968301545,168.0220406836314</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>-46.38297941848753,168.02112141321098</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>-46.38289107406087,168.02022680361387</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>-46.382899256087576,168.0193274792538</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0535/nzd0535.xlsx
+++ b/data/nzd0535/nzd0535.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N479"/>
+  <dimension ref="A1:N481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23438,6 +23438,102 @@
         <v>312.04</v>
       </c>
       <c r="N479" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>325.79</v>
+      </c>
+      <c r="C480" t="n">
+        <v>317.65</v>
+      </c>
+      <c r="D480" t="n">
+        <v>319.59</v>
+      </c>
+      <c r="E480" t="n">
+        <v>319.08</v>
+      </c>
+      <c r="F480" t="n">
+        <v>321.86</v>
+      </c>
+      <c r="G480" t="n">
+        <v>321.01</v>
+      </c>
+      <c r="H480" t="n">
+        <v>317.22</v>
+      </c>
+      <c r="I480" t="n">
+        <v>319.49</v>
+      </c>
+      <c r="J480" t="n">
+        <v>320.08</v>
+      </c>
+      <c r="K480" t="n">
+        <v>318.23</v>
+      </c>
+      <c r="L480" t="n">
+        <v>309.51</v>
+      </c>
+      <c r="M480" t="n">
+        <v>311.09</v>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>327.72</v>
+      </c>
+      <c r="C481" t="n">
+        <v>319.27</v>
+      </c>
+      <c r="D481" t="n">
+        <v>321.07</v>
+      </c>
+      <c r="E481" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="F481" t="n">
+        <v>322.19</v>
+      </c>
+      <c r="G481" t="n">
+        <v>321.76</v>
+      </c>
+      <c r="H481" t="n">
+        <v>319.29</v>
+      </c>
+      <c r="I481" t="n">
+        <v>319.43</v>
+      </c>
+      <c r="J481" t="n">
+        <v>320.51</v>
+      </c>
+      <c r="K481" t="n">
+        <v>318.95</v>
+      </c>
+      <c r="L481" t="n">
+        <v>309.99</v>
+      </c>
+      <c r="M481" t="n">
+        <v>311.49</v>
+      </c>
+      <c r="N481" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23454,7 +23550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B535"/>
+  <dimension ref="A1:B537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28807,6 +28903,26 @@
       </c>
       <c r="B535" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -28975,28 +29091,28 @@
         <v>0.1816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.175588834140402</v>
+        <v>0.1743839729936995</v>
       </c>
       <c r="J2" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06242088391731648</v>
+        <v>0.06211230320074324</v>
       </c>
       <c r="M2" t="n">
-        <v>3.668825535217538</v>
+        <v>3.658915855610247</v>
       </c>
       <c r="N2" t="n">
-        <v>26.23317271085456</v>
+        <v>26.13689041907323</v>
       </c>
       <c r="O2" t="n">
-        <v>5.121832944450118</v>
+        <v>5.112425101561217</v>
       </c>
       <c r="P2" t="n">
-        <v>323.6102450531363</v>
+        <v>323.6225429609059</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29053,28 +29169,28 @@
         <v>0.127</v>
       </c>
       <c r="I3" t="n">
-        <v>0.328658252451489</v>
+        <v>0.3280163904738216</v>
       </c>
       <c r="J3" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K3" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2283739379953386</v>
+        <v>0.2292241085231265</v>
       </c>
       <c r="M3" t="n">
-        <v>3.281488287736198</v>
+        <v>3.271249901641655</v>
       </c>
       <c r="N3" t="n">
-        <v>20.6741873418732</v>
+        <v>20.59332608492047</v>
       </c>
       <c r="O3" t="n">
-        <v>4.546887654415182</v>
+        <v>4.537987008015831</v>
       </c>
       <c r="P3" t="n">
-        <v>310.57853866362</v>
+        <v>310.5850888938455</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29131,28 +29247,28 @@
         <v>0.0954</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2350342869200435</v>
+        <v>0.2363509504348459</v>
       </c>
       <c r="J4" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K4" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1731398518651897</v>
+        <v>0.175916097979647</v>
       </c>
       <c r="M4" t="n">
-        <v>2.895876051428078</v>
+        <v>2.890259063614887</v>
       </c>
       <c r="N4" t="n">
-        <v>14.944331076965</v>
+        <v>14.89526140715487</v>
       </c>
       <c r="O4" t="n">
-        <v>3.865789838695969</v>
+        <v>3.859437965190641</v>
       </c>
       <c r="P4" t="n">
-        <v>312.492726684831</v>
+        <v>312.4792802160073</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29209,28 +29325,28 @@
         <v>0.1367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2520561914789583</v>
+        <v>0.2531715141964975</v>
       </c>
       <c r="J5" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K5" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1804836259967494</v>
+        <v>0.1830474900006133</v>
       </c>
       <c r="M5" t="n">
-        <v>2.898977378898013</v>
+        <v>2.892888629534836</v>
       </c>
       <c r="N5" t="n">
-        <v>16.3415626952788</v>
+        <v>16.28284495356685</v>
       </c>
       <c r="O5" t="n">
-        <v>4.042469875617974</v>
+        <v>4.035200732747611</v>
       </c>
       <c r="P5" t="n">
-        <v>311.6571910701689</v>
+        <v>311.645800880185</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29287,28 +29403,28 @@
         <v>0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1926226742268843</v>
+        <v>0.1945535112834601</v>
       </c>
       <c r="J6" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K6" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L6" t="n">
-        <v>0.162124927866009</v>
+        <v>0.1657906395784068</v>
       </c>
       <c r="M6" t="n">
-        <v>2.499637190878577</v>
+        <v>2.498239904815446</v>
       </c>
       <c r="N6" t="n">
-        <v>10.88252541065684</v>
+        <v>10.8607677800606</v>
       </c>
       <c r="O6" t="n">
-        <v>3.298867292065087</v>
+        <v>3.295567899476599</v>
       </c>
       <c r="P6" t="n">
-        <v>314.5465372528136</v>
+        <v>314.5268351680196</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29365,28 +29481,28 @@
         <v>0.1233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.132828008814176</v>
+        <v>0.1332975692325243</v>
       </c>
       <c r="J7" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K7" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09901150209097065</v>
+        <v>0.1004315124268863</v>
       </c>
       <c r="M7" t="n">
-        <v>2.288322346171951</v>
+        <v>2.281123840235694</v>
       </c>
       <c r="N7" t="n">
-        <v>9.111677130054515</v>
+        <v>9.075614071617581</v>
       </c>
       <c r="O7" t="n">
-        <v>3.018555470759899</v>
+        <v>3.01257598603215</v>
       </c>
       <c r="P7" t="n">
-        <v>317.2956535255313</v>
+        <v>317.2908607799155</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29443,28 +29559,28 @@
         <v>0.106</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0002443630857558775</v>
+        <v>-0.0005708518037994244</v>
       </c>
       <c r="J8" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K8" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L8" t="n">
-        <v>3.12106396616052e-07</v>
+        <v>1.717798934097736e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.552960057804724</v>
+        <v>2.546820668912611</v>
       </c>
       <c r="N8" t="n">
-        <v>10.83795676527657</v>
+        <v>10.79794861236713</v>
       </c>
       <c r="O8" t="n">
-        <v>3.292105217831983</v>
+        <v>3.286023221519764</v>
       </c>
       <c r="P8" t="n">
-        <v>318.668067103757</v>
+        <v>318.6713963358343</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29521,28 +29637,28 @@
         <v>0.1023</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07814959939141534</v>
+        <v>-0.07829795086200829</v>
       </c>
       <c r="J9" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K9" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03196332071448504</v>
+        <v>0.03236062161844966</v>
       </c>
       <c r="M9" t="n">
-        <v>2.637454094508729</v>
+        <v>2.627171557058451</v>
       </c>
       <c r="N9" t="n">
-        <v>10.47785659081397</v>
+        <v>10.43434151180413</v>
       </c>
       <c r="O9" t="n">
-        <v>3.236951743664704</v>
+        <v>3.230223136534708</v>
       </c>
       <c r="P9" t="n">
-        <v>321.7100351739789</v>
+        <v>321.7115500003344</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29599,28 +29715,28 @@
         <v>0.1526</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08413000209255597</v>
+        <v>-0.0856835339391889</v>
       </c>
       <c r="J10" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K10" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02867675915911505</v>
+        <v>0.02994087469960094</v>
       </c>
       <c r="M10" t="n">
-        <v>2.863714003560974</v>
+        <v>2.859455291194384</v>
       </c>
       <c r="N10" t="n">
-        <v>13.5804614728158</v>
+        <v>13.53929460198455</v>
       </c>
       <c r="O10" t="n">
-        <v>3.685167767255081</v>
+        <v>3.679578046730977</v>
       </c>
       <c r="P10" t="n">
-        <v>324.4433629212795</v>
+        <v>324.459223918621</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29677,28 +29793,28 @@
         <v>0.1109</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1410448045519885</v>
+        <v>-0.1424409924567241</v>
       </c>
       <c r="J11" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K11" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08593346752310416</v>
+        <v>0.08812707995769997</v>
       </c>
       <c r="M11" t="n">
-        <v>2.764882727883734</v>
+        <v>2.759969054584623</v>
       </c>
       <c r="N11" t="n">
-        <v>11.98694949058036</v>
+        <v>11.94985116717789</v>
       </c>
       <c r="O11" t="n">
-        <v>3.462217423932292</v>
+        <v>3.456855676359355</v>
       </c>
       <c r="P11" t="n">
-        <v>324.0405413481449</v>
+        <v>324.0547952217898</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29755,28 +29871,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1862972139444906</v>
+        <v>-0.1872580841230887</v>
       </c>
       <c r="J12" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K12" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L12" t="n">
-        <v>0.102002703494765</v>
+        <v>0.1037489825365597</v>
       </c>
       <c r="M12" t="n">
-        <v>3.328429119634078</v>
+        <v>3.319756452817797</v>
       </c>
       <c r="N12" t="n">
-        <v>17.30832669739655</v>
+        <v>17.24227402253873</v>
       </c>
       <c r="O12" t="n">
-        <v>4.160327715144151</v>
+        <v>4.152381728904357</v>
       </c>
       <c r="P12" t="n">
-        <v>315.8565859052021</v>
+        <v>315.8663955999895</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29833,28 +29949,28 @@
         <v>0.0591</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2011146148138494</v>
+        <v>-0.2029015408831652</v>
       </c>
       <c r="J13" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K13" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1082309218340276</v>
+        <v>0.1107262821400243</v>
       </c>
       <c r="M13" t="n">
-        <v>3.408591112192336</v>
+        <v>3.403268191473011</v>
       </c>
       <c r="N13" t="n">
-        <v>18.87849337651534</v>
+        <v>18.82014675430275</v>
       </c>
       <c r="O13" t="n">
-        <v>4.344938823103881</v>
+        <v>4.33821930684731</v>
       </c>
       <c r="P13" t="n">
-        <v>318.8116309266194</v>
+        <v>318.8298749808019</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29892,7 +30008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N479"/>
+  <dimension ref="A1:N481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64375,6 +64491,150 @@
         </is>
       </c>
     </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>-46.38424315186591,168.02902408022138</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>-46.38402421623932,168.02818182339604</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>-46.383892162509625,168.0273026802836</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-46.38373899120806,168.02643250278376</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>-46.38361417665764,168.02555028514087</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>-46.38345807399917,168.02468135184867</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>-46.383276630701125,168.02382317850766</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>-46.38314741902938,168.02294282689206</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>-46.38300179928487,168.02204414808628</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>-46.382965970046946,168.02112264236533</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>-46.382882192498776,168.02022747487305</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>-46.38289073338551,168.01932812348738</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>-46.38425978708468,168.0290170177143</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>-46.384038179443195,168.02817589516826</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>-46.383904918980754,168.02729726424957</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-46.38374950664824,168.0264280381183</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>-46.38361702098993,168.025549077458</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>-46.383464538372756,168.02467860705536</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>-46.383294472323435,168.0238156027202</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>-46.38314690188236,168.022943046485</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>-46.38300559973936,168.02204314827736</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>-46.38297242529843,168.02112205237134</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>-46.38288649871071,168.0202271494141</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>-46.38289432189165,168.01932785223119</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0535/nzd0535.xlsx
+++ b/data/nzd0535/nzd0535.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N481"/>
+  <dimension ref="A1:N483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23534,6 +23534,102 @@
         <v>311.49</v>
       </c>
       <c r="N481" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:21:03+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>327.22</v>
+      </c>
+      <c r="C482" t="n">
+        <v>319.37</v>
+      </c>
+      <c r="D482" t="n">
+        <v>319.55</v>
+      </c>
+      <c r="E482" t="n">
+        <v>319.16</v>
+      </c>
+      <c r="F482" t="n">
+        <v>321.08</v>
+      </c>
+      <c r="G482" t="n">
+        <v>320.54</v>
+      </c>
+      <c r="H482" t="n">
+        <v>318.7</v>
+      </c>
+      <c r="I482" t="n">
+        <v>317.01</v>
+      </c>
+      <c r="J482" t="n">
+        <v>319.18</v>
+      </c>
+      <c r="K482" t="n">
+        <v>317.09</v>
+      </c>
+      <c r="L482" t="n">
+        <v>308.01</v>
+      </c>
+      <c r="M482" t="n">
+        <v>309.61</v>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:27:11+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="C483" t="n">
+        <v>320.18</v>
+      </c>
+      <c r="D483" t="n">
+        <v>320.21</v>
+      </c>
+      <c r="E483" t="n">
+        <v>320.09</v>
+      </c>
+      <c r="F483" t="n">
+        <v>321.7</v>
+      </c>
+      <c r="G483" t="n">
+        <v>320.67</v>
+      </c>
+      <c r="H483" t="n">
+        <v>319.03</v>
+      </c>
+      <c r="I483" t="n">
+        <v>317.19</v>
+      </c>
+      <c r="J483" t="n">
+        <v>319.43</v>
+      </c>
+      <c r="K483" t="n">
+        <v>317.01</v>
+      </c>
+      <c r="L483" t="n">
+        <v>308.35</v>
+      </c>
+      <c r="M483" t="n">
+        <v>309.94</v>
+      </c>
+      <c r="N483" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23550,7 +23646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B537"/>
+  <dimension ref="A1:B539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28923,6 +29019,26 @@
       </c>
       <c r="B537" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -29091,28 +29207,28 @@
         <v>0.1816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1743839729936995</v>
+        <v>0.1738089494113579</v>
       </c>
       <c r="J2" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K2" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06211230320074324</v>
+        <v>0.06224073538297348</v>
       </c>
       <c r="M2" t="n">
-        <v>3.658915855610247</v>
+        <v>3.646290043248781</v>
       </c>
       <c r="N2" t="n">
-        <v>26.13689041907323</v>
+        <v>26.03090293877789</v>
       </c>
       <c r="O2" t="n">
-        <v>5.112425101561217</v>
+        <v>5.102048896157101</v>
       </c>
       <c r="P2" t="n">
-        <v>323.6225429609059</v>
+        <v>323.6284251309388</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29169,28 +29285,28 @@
         <v>0.127</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3280163904738216</v>
+        <v>0.3284289816441271</v>
       </c>
       <c r="J3" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K3" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2292241085231265</v>
+        <v>0.2312323859259038</v>
       </c>
       <c r="M3" t="n">
-        <v>3.271249901641655</v>
+        <v>3.25972647967157</v>
       </c>
       <c r="N3" t="n">
-        <v>20.59332608492047</v>
+        <v>20.50962322425083</v>
       </c>
       <c r="O3" t="n">
-        <v>4.537987008015831</v>
+        <v>4.528755151722251</v>
       </c>
       <c r="P3" t="n">
-        <v>310.5850888938455</v>
+        <v>310.5808661302248</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29247,28 +29363,28 @@
         <v>0.0954</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2363509504348459</v>
+        <v>0.237272796875728</v>
       </c>
       <c r="J4" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K4" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L4" t="n">
-        <v>0.175916097979647</v>
+        <v>0.1782904383644486</v>
       </c>
       <c r="M4" t="n">
-        <v>2.890259063614887</v>
+        <v>2.882799495394913</v>
       </c>
       <c r="N4" t="n">
-        <v>14.89526140715487</v>
+        <v>14.8393371663333</v>
       </c>
       <c r="O4" t="n">
-        <v>3.859437965190641</v>
+        <v>3.852186024367632</v>
       </c>
       <c r="P4" t="n">
-        <v>312.4792802160073</v>
+        <v>312.469847380637</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29325,28 +29441,28 @@
         <v>0.1367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2531715141964975</v>
+        <v>0.2541971047538191</v>
       </c>
       <c r="J5" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K5" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1830474900006133</v>
+        <v>0.1855307911313729</v>
       </c>
       <c r="M5" t="n">
-        <v>2.892888629534836</v>
+        <v>2.886402620184329</v>
       </c>
       <c r="N5" t="n">
-        <v>16.28284495356685</v>
+        <v>16.22288871443865</v>
       </c>
       <c r="O5" t="n">
-        <v>4.035200732747611</v>
+        <v>4.027764729280827</v>
       </c>
       <c r="P5" t="n">
-        <v>311.645800880185</v>
+        <v>311.6353061342394</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29403,28 +29519,28 @@
         <v>0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1945535112834601</v>
+        <v>0.1959298234653088</v>
       </c>
       <c r="J6" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K6" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1657906395784068</v>
+        <v>0.1688327290218113</v>
       </c>
       <c r="M6" t="n">
-        <v>2.498239904815446</v>
+        <v>2.494252834527723</v>
       </c>
       <c r="N6" t="n">
-        <v>10.8607677800606</v>
+        <v>10.82815236073274</v>
       </c>
       <c r="O6" t="n">
-        <v>3.295567899476599</v>
+        <v>3.290615802662587</v>
       </c>
       <c r="P6" t="n">
-        <v>314.5268351680196</v>
+        <v>314.5127617120975</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29481,28 +29597,28 @@
         <v>0.1233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1332975692325243</v>
+        <v>0.1331289416019642</v>
       </c>
       <c r="J7" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K7" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1004315124268863</v>
+        <v>0.1010059836726482</v>
       </c>
       <c r="M7" t="n">
-        <v>2.281123840235694</v>
+        <v>2.272529550448862</v>
       </c>
       <c r="N7" t="n">
-        <v>9.075614071617581</v>
+        <v>9.03807888917507</v>
       </c>
       <c r="O7" t="n">
-        <v>3.01257598603215</v>
+        <v>3.006339782721685</v>
       </c>
       <c r="P7" t="n">
-        <v>317.2908607799155</v>
+        <v>317.2925846977452</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29559,28 +29675,28 @@
         <v>0.106</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0005708518037994244</v>
+        <v>-0.0004032902553445896</v>
       </c>
       <c r="J8" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K8" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L8" t="n">
-        <v>1.717798934097736e-06</v>
+        <v>8.650004527099853e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>2.546820668912611</v>
+        <v>2.537017610828538</v>
       </c>
       <c r="N8" t="n">
-        <v>10.79794861236713</v>
+        <v>10.75343123091982</v>
       </c>
       <c r="O8" t="n">
-        <v>3.286023221519764</v>
+        <v>3.279242478213501</v>
       </c>
       <c r="P8" t="n">
-        <v>318.6713963358343</v>
+        <v>318.6696813887066</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29637,28 +29753,28 @@
         <v>0.1023</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07829795086200829</v>
+        <v>-0.08032998813073948</v>
       </c>
       <c r="J9" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K9" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03236062161844966</v>
+        <v>0.03421382530675354</v>
       </c>
       <c r="M9" t="n">
-        <v>2.627171557058451</v>
+        <v>2.625923937601517</v>
       </c>
       <c r="N9" t="n">
-        <v>10.43434151180413</v>
+        <v>10.41748951003276</v>
       </c>
       <c r="O9" t="n">
-        <v>3.230223136534708</v>
+        <v>3.227613593668357</v>
       </c>
       <c r="P9" t="n">
-        <v>321.7115500003344</v>
+        <v>321.7323399643559</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29715,28 +29831,28 @@
         <v>0.1526</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0856835339391889</v>
+        <v>-0.08799285074445044</v>
       </c>
       <c r="J10" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K10" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02994087469960094</v>
+        <v>0.03172008935016468</v>
       </c>
       <c r="M10" t="n">
-        <v>2.859455291194384</v>
+        <v>2.858976795251824</v>
       </c>
       <c r="N10" t="n">
-        <v>13.53929460198455</v>
+        <v>13.51728937093616</v>
       </c>
       <c r="O10" t="n">
-        <v>3.679578046730977</v>
+        <v>3.676586646733102</v>
       </c>
       <c r="P10" t="n">
-        <v>324.459223918621</v>
+        <v>324.4828506775814</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29793,28 +29909,28 @@
         <v>0.1109</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1424409924567241</v>
+        <v>-0.1450346391774797</v>
       </c>
       <c r="J11" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K11" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08812707995769997</v>
+        <v>0.09150987043637215</v>
       </c>
       <c r="M11" t="n">
-        <v>2.759969054584623</v>
+        <v>2.760682868125587</v>
       </c>
       <c r="N11" t="n">
-        <v>11.94985116717789</v>
+        <v>11.94329242982715</v>
       </c>
       <c r="O11" t="n">
-        <v>3.456855676359355</v>
+        <v>3.455906889635072</v>
       </c>
       <c r="P11" t="n">
-        <v>324.0547952217898</v>
+        <v>324.0813316253852</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29871,28 +29987,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1872580841230887</v>
+        <v>-0.1894468756213816</v>
       </c>
       <c r="J12" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K12" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1037489825365597</v>
+        <v>0.1066056668960955</v>
       </c>
       <c r="M12" t="n">
-        <v>3.319756452817797</v>
+        <v>3.317717953409236</v>
       </c>
       <c r="N12" t="n">
-        <v>17.24227402253873</v>
+        <v>17.20149177688953</v>
       </c>
       <c r="O12" t="n">
-        <v>4.152381728904357</v>
+        <v>4.147468116440382</v>
       </c>
       <c r="P12" t="n">
-        <v>315.8663955999895</v>
+        <v>315.8887890744634</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29949,28 +30065,28 @@
         <v>0.0591</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2029015408831652</v>
+        <v>-0.2058538614562667</v>
       </c>
       <c r="J13" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K13" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1107262821400243</v>
+        <v>0.114201417788554</v>
       </c>
       <c r="M13" t="n">
-        <v>3.403268191473011</v>
+        <v>3.403847952656882</v>
       </c>
       <c r="N13" t="n">
-        <v>18.82014675430275</v>
+        <v>18.79792172584482</v>
       </c>
       <c r="O13" t="n">
-        <v>4.33821930684731</v>
+        <v>4.335657012016151</v>
       </c>
       <c r="P13" t="n">
-        <v>318.8298749808019</v>
+        <v>318.8600803191525</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30008,7 +30124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N481"/>
+  <dimension ref="A1:N483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64635,6 +64751,150 @@
         </is>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:21:03+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>-46.38425547744257,168.02901884737977</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>-46.38403904136936,168.02817552922812</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>-46.38389181774013,168.0273028266629</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>-46.38373968074513,168.02643221001887</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>-46.38360745369033,168.02555313966346</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>-46.38345402299167,168.0246830719188</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-46.38328938703019,168.02381776200318</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-46.38312604361893,168.0229519033967</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>-46.38299384484518,168.02204624070913</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>-46.38295574923209,168.02112357652203</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>-46.382868735586484,168.02022849193182</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>-46.382877455912784,168.0193291271349</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:27:11+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>-46.384260562820245,168.02901668837447</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>-46.38404602297113,168.0281725651129</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>-46.38389750643676,168.0273004114048</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-46.383747696613476,168.0264288066264</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>-46.383612797587425,168.02555087068404</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>-46.38345514348311,168.02468259615475</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>-46.38329223134675,168.02381655426868</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-46.38312759506004,168.02295124461838</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>-46.38299605441176,168.0220456594251</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>-46.382955031981915,168.02112364207687</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>-46.38287178581994,168.0202282613986</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>-46.38288041643037,168.01932890334868</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0535/nzd0535.xlsx
+++ b/data/nzd0535/nzd0535.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N483"/>
+  <dimension ref="A1:N484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23632,6 +23632,54 @@
       <c r="N483" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>332.4</v>
+      </c>
+      <c r="C484" t="n">
+        <v>323.87</v>
+      </c>
+      <c r="D484" t="n">
+        <v>322.77</v>
+      </c>
+      <c r="E484" t="n">
+        <v>321.96</v>
+      </c>
+      <c r="F484" t="n">
+        <v>321.87</v>
+      </c>
+      <c r="G484" t="n">
+        <v>319.3</v>
+      </c>
+      <c r="H484" t="n">
+        <v>318.1</v>
+      </c>
+      <c r="I484" t="n">
+        <v>314.94</v>
+      </c>
+      <c r="J484" t="n">
+        <v>318.1</v>
+      </c>
+      <c r="K484" t="n">
+        <v>314.14</v>
+      </c>
+      <c r="L484" t="n">
+        <v>305.77</v>
+      </c>
+      <c r="M484" t="n">
+        <v>308.3</v>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23646,7 +23694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B539"/>
+  <dimension ref="A1:B540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29039,6 +29087,16 @@
       </c>
       <c r="B539" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -29207,28 +29265,28 @@
         <v>0.1816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1738089494113579</v>
+        <v>0.175482020819089</v>
       </c>
       <c r="J2" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K2" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06224073538297348</v>
+        <v>0.06355649498214211</v>
       </c>
       <c r="M2" t="n">
-        <v>3.646290043248781</v>
+        <v>3.648532754882839</v>
       </c>
       <c r="N2" t="n">
-        <v>26.03090293877789</v>
+        <v>26.01239360798523</v>
       </c>
       <c r="O2" t="n">
-        <v>5.102048896157101</v>
+        <v>5.100234662050878</v>
       </c>
       <c r="P2" t="n">
-        <v>323.6284251309388</v>
+        <v>323.6111812490716</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29285,28 +29343,28 @@
         <v>0.127</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3284289816441271</v>
+        <v>0.3302660541854321</v>
       </c>
       <c r="J3" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K3" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2312323859259038</v>
+        <v>0.2336585656229205</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25972647967157</v>
+        <v>3.262100046810895</v>
       </c>
       <c r="N3" t="n">
-        <v>20.50962322425083</v>
+        <v>20.50982225099915</v>
       </c>
       <c r="O3" t="n">
-        <v>4.528755151722251</v>
+        <v>4.528777125339593</v>
       </c>
       <c r="P3" t="n">
-        <v>310.5808661302248</v>
+        <v>310.5619319342679</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29363,28 +29421,28 @@
         <v>0.0954</v>
       </c>
       <c r="I4" t="n">
-        <v>0.237272796875728</v>
+        <v>0.2388821685255807</v>
       </c>
       <c r="J4" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K4" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1782904383644486</v>
+        <v>0.1806223292886825</v>
       </c>
       <c r="M4" t="n">
-        <v>2.882799495394913</v>
+        <v>2.884623013579904</v>
       </c>
       <c r="N4" t="n">
-        <v>14.8393371663333</v>
+        <v>14.84135561746838</v>
       </c>
       <c r="O4" t="n">
-        <v>3.852186024367632</v>
+        <v>3.852448003214109</v>
       </c>
       <c r="P4" t="n">
-        <v>312.469847380637</v>
+        <v>312.453260034465</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29441,28 +29499,28 @@
         <v>0.1367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2541971047538191</v>
+        <v>0.2556338265119764</v>
       </c>
       <c r="J5" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K5" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1855307911313729</v>
+        <v>0.1876841045557254</v>
       </c>
       <c r="M5" t="n">
-        <v>2.886402620184329</v>
+        <v>2.888067043409982</v>
       </c>
       <c r="N5" t="n">
-        <v>16.22288871443865</v>
+        <v>16.21539455838083</v>
       </c>
       <c r="O5" t="n">
-        <v>4.027764729280827</v>
+        <v>4.026834309774967</v>
       </c>
       <c r="P5" t="n">
-        <v>311.6353061342394</v>
+        <v>311.6204982425025</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29519,28 +29577,28 @@
         <v>0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1959298234653088</v>
+        <v>0.1967929724470038</v>
       </c>
       <c r="J6" t="n">
+        <v>483</v>
+      </c>
+      <c r="K6" t="n">
         <v>482</v>
       </c>
-      <c r="K6" t="n">
-        <v>481</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1688327290218113</v>
+        <v>0.1705855778164612</v>
       </c>
       <c r="M6" t="n">
-        <v>2.494252834527723</v>
+        <v>2.493226425904927</v>
       </c>
       <c r="N6" t="n">
-        <v>10.82815236073274</v>
+        <v>10.81512937569632</v>
       </c>
       <c r="O6" t="n">
-        <v>3.290615802662587</v>
+        <v>3.288636400652452</v>
       </c>
       <c r="P6" t="n">
-        <v>314.5127617120975</v>
+        <v>314.5038709822848</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29597,28 +29655,28 @@
         <v>0.1233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1331289416019642</v>
+        <v>0.1325095044574194</v>
       </c>
       <c r="J7" t="n">
+        <v>483</v>
+      </c>
+      <c r="K7" t="n">
         <v>482</v>
       </c>
-      <c r="K7" t="n">
-        <v>481</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1010059836726482</v>
+        <v>0.1005216886767618</v>
       </c>
       <c r="M7" t="n">
-        <v>2.272529550448862</v>
+        <v>2.271055426075749</v>
       </c>
       <c r="N7" t="n">
-        <v>9.03807888917507</v>
+        <v>9.024190525935342</v>
       </c>
       <c r="O7" t="n">
-        <v>3.006339782721685</v>
+        <v>3.00402904878354</v>
       </c>
       <c r="P7" t="n">
-        <v>317.2925846977452</v>
+        <v>317.2989651122563</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29675,28 +29733,28 @@
         <v>0.106</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0004032902553445896</v>
+        <v>-0.0006275417165248549</v>
       </c>
       <c r="J8" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K8" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L8" t="n">
-        <v>8.650004527099853e-07</v>
+        <v>2.103802721031833e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.537017610828538</v>
+        <v>2.533046353400601</v>
       </c>
       <c r="N8" t="n">
-        <v>10.75343123091982</v>
+        <v>10.73180310853906</v>
       </c>
       <c r="O8" t="n">
-        <v>3.279242478213501</v>
+        <v>3.275943086889493</v>
       </c>
       <c r="P8" t="n">
-        <v>318.6696813887066</v>
+        <v>318.6719926861726</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29753,28 +29811,28 @@
         <v>0.1023</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08032998813073948</v>
+        <v>-0.08220879712232795</v>
       </c>
       <c r="J9" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K9" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03421382530675354</v>
+        <v>0.03578339139056208</v>
       </c>
       <c r="M9" t="n">
-        <v>2.625923937601517</v>
+        <v>2.62935566600536</v>
       </c>
       <c r="N9" t="n">
-        <v>10.41748951003276</v>
+        <v>10.44054372027611</v>
       </c>
       <c r="O9" t="n">
-        <v>3.227613593668357</v>
+        <v>3.231183021785691</v>
       </c>
       <c r="P9" t="n">
-        <v>321.7323399643559</v>
+        <v>321.7517043263027</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29831,28 +29889,28 @@
         <v>0.1526</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08799285074445044</v>
+        <v>-0.08962141473883613</v>
       </c>
       <c r="J10" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K10" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03172008935016468</v>
+        <v>0.0329311427900254</v>
       </c>
       <c r="M10" t="n">
-        <v>2.858976795251824</v>
+        <v>2.861043794853962</v>
       </c>
       <c r="N10" t="n">
-        <v>13.51728937093616</v>
+        <v>13.52283055125667</v>
       </c>
       <c r="O10" t="n">
-        <v>3.676586646733102</v>
+        <v>3.677340146254718</v>
       </c>
       <c r="P10" t="n">
-        <v>324.4828506775814</v>
+        <v>324.4996358339129</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29909,28 +29967,28 @@
         <v>0.1109</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1450346391774797</v>
+        <v>-0.1474895576354581</v>
       </c>
       <c r="J11" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K11" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09150987043637215</v>
+        <v>0.09418157583071551</v>
       </c>
       <c r="M11" t="n">
-        <v>2.760682868125587</v>
+        <v>2.766420659035868</v>
       </c>
       <c r="N11" t="n">
-        <v>11.94329242982715</v>
+        <v>11.99474896220194</v>
       </c>
       <c r="O11" t="n">
-        <v>3.455906889635072</v>
+        <v>3.463343610183943</v>
       </c>
       <c r="P11" t="n">
-        <v>324.0813316253852</v>
+        <v>324.1066337874373</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29987,28 +30045,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1894468756213816</v>
+        <v>-0.1914954771852707</v>
       </c>
       <c r="J12" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K12" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1066056668960955</v>
+        <v>0.1088112931800729</v>
       </c>
       <c r="M12" t="n">
-        <v>3.317717953409236</v>
+        <v>3.321704844532571</v>
       </c>
       <c r="N12" t="n">
-        <v>17.20149177688953</v>
+        <v>17.2189301652699</v>
       </c>
       <c r="O12" t="n">
-        <v>4.147468116440382</v>
+        <v>4.149569877140268</v>
       </c>
       <c r="P12" t="n">
-        <v>315.8887890744634</v>
+        <v>315.9099034412486</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30065,28 +30123,28 @@
         <v>0.0591</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2058538614562667</v>
+        <v>-0.2079035581349168</v>
       </c>
       <c r="J13" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K13" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L13" t="n">
-        <v>0.114201417788554</v>
+        <v>0.1163958424093346</v>
       </c>
       <c r="M13" t="n">
-        <v>3.403847952656882</v>
+        <v>3.407026723651076</v>
       </c>
       <c r="N13" t="n">
-        <v>18.79792172584482</v>
+        <v>18.81211161135108</v>
       </c>
       <c r="O13" t="n">
-        <v>4.335657012016151</v>
+        <v>4.337293120294163</v>
       </c>
       <c r="P13" t="n">
-        <v>318.8600803191525</v>
+        <v>318.8812059729811</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30124,7 +30182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N483"/>
+  <dimension ref="A1:N484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64895,6 +64953,78 @@
         </is>
       </c>
     </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>-46.38430012533273,168.02899989203</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>-46.38407782804442,168.0281590619108</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>-46.38391957168362,168.027291043126</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-46.383763814541844,168.0264219632426</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>-46.38361426284952,168.02555024854445</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>-46.383443335227035,168.0246876099748</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>-46.38328421554547,168.0238199578837</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>-46.38310820204569,168.02295947934422</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>-46.38298429951746,168.02204875185564</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>-46.382929300632036,168.02112599385504</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>-46.3828486399307,168.02023001073815</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>-46.38286570355513,168.01933001549793</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0535/nzd0535.xlsx
+++ b/data/nzd0535/nzd0535.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N484"/>
+  <dimension ref="A1:N485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23680,6 +23680,54 @@
       <c r="N484" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>332.81</v>
+      </c>
+      <c r="C485" t="n">
+        <v>324.2</v>
+      </c>
+      <c r="D485" t="n">
+        <v>323.6</v>
+      </c>
+      <c r="E485" t="n">
+        <v>321.87</v>
+      </c>
+      <c r="F485" t="n">
+        <v>321.49</v>
+      </c>
+      <c r="G485" t="n">
+        <v>319.24</v>
+      </c>
+      <c r="H485" t="n">
+        <v>318.31</v>
+      </c>
+      <c r="I485" t="n">
+        <v>316.09</v>
+      </c>
+      <c r="J485" t="n">
+        <v>319.28</v>
+      </c>
+      <c r="K485" t="n">
+        <v>315.08</v>
+      </c>
+      <c r="L485" t="n">
+        <v>306.77</v>
+      </c>
+      <c r="M485" t="n">
+        <v>309.03</v>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B540"/>
+  <dimension ref="A1:B541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29097,6 +29145,16 @@
       </c>
       <c r="B540" t="n">
         <v>-0.75</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -29265,28 +29323,28 @@
         <v>0.1816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.175482020819089</v>
+        <v>0.1772990706832872</v>
       </c>
       <c r="J2" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K2" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06355649498214211</v>
+        <v>0.06496886306257688</v>
       </c>
       <c r="M2" t="n">
-        <v>3.648532754882839</v>
+        <v>3.651744287993321</v>
       </c>
       <c r="N2" t="n">
-        <v>26.01239360798523</v>
+        <v>26.00068699585749</v>
       </c>
       <c r="O2" t="n">
-        <v>5.100234662050878</v>
+        <v>5.099086878634006</v>
       </c>
       <c r="P2" t="n">
-        <v>323.6111812490716</v>
+        <v>323.5924351684887</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29343,28 +29401,28 @@
         <v>0.127</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3302660541854321</v>
+        <v>0.3322108580866206</v>
       </c>
       <c r="J3" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K3" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2336585656229205</v>
+        <v>0.2361560545626723</v>
       </c>
       <c r="M3" t="n">
-        <v>3.262100046810895</v>
+        <v>3.265091048998805</v>
       </c>
       <c r="N3" t="n">
-        <v>20.50982225099915</v>
+        <v>20.51560365096359</v>
       </c>
       <c r="O3" t="n">
-        <v>4.528777125339593</v>
+        <v>4.529415376289041</v>
       </c>
       <c r="P3" t="n">
-        <v>310.5619319342679</v>
+        <v>310.5418678450165</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29421,28 +29479,28 @@
         <v>0.0954</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2388821685255807</v>
+        <v>0.2408054205804444</v>
       </c>
       <c r="J4" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K4" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1806223292886825</v>
+        <v>0.1832068010077328</v>
       </c>
       <c r="M4" t="n">
-        <v>2.884623013579904</v>
+        <v>2.887937991510613</v>
       </c>
       <c r="N4" t="n">
-        <v>14.84135561746838</v>
+        <v>14.85778730939484</v>
       </c>
       <c r="O4" t="n">
-        <v>3.852448003214109</v>
+        <v>3.854580043194698</v>
       </c>
       <c r="P4" t="n">
-        <v>312.453260034465</v>
+        <v>312.4334182905965</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29499,28 +29557,28 @@
         <v>0.1367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2556338265119764</v>
+        <v>0.2570148987749143</v>
       </c>
       <c r="J5" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K5" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1876841045557254</v>
+        <v>0.189794035212921</v>
       </c>
       <c r="M5" t="n">
-        <v>2.888067043409982</v>
+        <v>2.889426303845489</v>
       </c>
       <c r="N5" t="n">
-        <v>16.21539455838083</v>
+        <v>16.20617684938679</v>
       </c>
       <c r="O5" t="n">
-        <v>4.026834309774967</v>
+        <v>4.025689611654975</v>
       </c>
       <c r="P5" t="n">
-        <v>311.6204982425025</v>
+        <v>311.6062500413706</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29577,28 +29635,28 @@
         <v>0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1967929724470038</v>
+        <v>0.197493167324552</v>
       </c>
       <c r="J6" t="n">
+        <v>484</v>
+      </c>
+      <c r="K6" t="n">
         <v>483</v>
       </c>
-      <c r="K6" t="n">
-        <v>482</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1705855778164612</v>
+        <v>0.1721510035936233</v>
       </c>
       <c r="M6" t="n">
-        <v>2.493226425904927</v>
+        <v>2.4914514347894</v>
       </c>
       <c r="N6" t="n">
-        <v>10.81512937569632</v>
+        <v>10.79899602540532</v>
       </c>
       <c r="O6" t="n">
-        <v>3.288636400652452</v>
+        <v>3.286182591610716</v>
       </c>
       <c r="P6" t="n">
-        <v>314.5038709822848</v>
+        <v>314.4966516820999</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29655,28 +29713,28 @@
         <v>0.1233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1325095044574194</v>
+        <v>0.1318728547354939</v>
       </c>
       <c r="J7" t="n">
+        <v>484</v>
+      </c>
+      <c r="K7" t="n">
         <v>483</v>
       </c>
-      <c r="K7" t="n">
-        <v>482</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1005216886767618</v>
+        <v>0.1000069187791776</v>
       </c>
       <c r="M7" t="n">
-        <v>2.271055426075749</v>
+        <v>2.269702295279082</v>
       </c>
       <c r="N7" t="n">
-        <v>9.024190525935342</v>
+        <v>9.01068075611972</v>
       </c>
       <c r="O7" t="n">
-        <v>3.00402904878354</v>
+        <v>3.001779598191666</v>
       </c>
       <c r="P7" t="n">
-        <v>317.2989651122563</v>
+        <v>317.3055292354776</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29733,28 +29791,28 @@
         <v>0.106</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0006275417165248549</v>
+        <v>-0.0007676352572946861</v>
       </c>
       <c r="J8" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K8" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L8" t="n">
-        <v>2.103802721031833e-06</v>
+        <v>3.162095290609734e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.533046353400601</v>
+        <v>2.528611306967457</v>
       </c>
       <c r="N8" t="n">
-        <v>10.73180310853906</v>
+        <v>10.70987984916374</v>
       </c>
       <c r="O8" t="n">
-        <v>3.275943086889493</v>
+        <v>3.27259527732406</v>
       </c>
       <c r="P8" t="n">
-        <v>318.6719926861726</v>
+        <v>318.67343799863</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29811,28 +29869,28 @@
         <v>0.1023</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08220879712232795</v>
+        <v>-0.08360372775280638</v>
       </c>
       <c r="J9" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K9" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03578339139056208</v>
+        <v>0.03703862810548619</v>
       </c>
       <c r="M9" t="n">
-        <v>2.62935566600536</v>
+        <v>2.630555161298583</v>
       </c>
       <c r="N9" t="n">
-        <v>10.44054372027611</v>
+        <v>10.44374734563049</v>
       </c>
       <c r="O9" t="n">
-        <v>3.231183021785691</v>
+        <v>3.231678719432129</v>
       </c>
       <c r="P9" t="n">
-        <v>321.7517043263027</v>
+        <v>321.7660955009873</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29889,28 +29947,28 @@
         <v>0.1526</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08962141473883613</v>
+        <v>-0.09075959015939136</v>
       </c>
       <c r="J10" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K10" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0329311427900254</v>
+        <v>0.03385166962370278</v>
       </c>
       <c r="M10" t="n">
-        <v>2.861043794853962</v>
+        <v>2.860715003840617</v>
       </c>
       <c r="N10" t="n">
-        <v>13.52283055125667</v>
+        <v>13.51138484902885</v>
       </c>
       <c r="O10" t="n">
-        <v>3.677340146254718</v>
+        <v>3.675783569394265</v>
       </c>
       <c r="P10" t="n">
-        <v>324.4996358339129</v>
+        <v>324.5113781248492</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29967,28 +30025,28 @@
         <v>0.1109</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1474895576354581</v>
+        <v>-0.1495367867602204</v>
       </c>
       <c r="J11" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K11" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09418157583071551</v>
+        <v>0.09656492015055507</v>
       </c>
       <c r="M11" t="n">
-        <v>2.766420659035868</v>
+        <v>2.770270711628162</v>
       </c>
       <c r="N11" t="n">
-        <v>11.99474896220194</v>
+        <v>12.02332955191757</v>
       </c>
       <c r="O11" t="n">
-        <v>3.463343610183943</v>
+        <v>3.467467310865031</v>
       </c>
       <c r="P11" t="n">
-        <v>324.1066337874373</v>
+        <v>324.1277545738838</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30045,28 +30103,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1914954771852707</v>
+        <v>-0.1931172809248725</v>
       </c>
       <c r="J12" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K12" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1088112931800729</v>
+        <v>0.1107091863621846</v>
       </c>
       <c r="M12" t="n">
-        <v>3.321704844532571</v>
+        <v>3.323460400010269</v>
       </c>
       <c r="N12" t="n">
-        <v>17.2189301652699</v>
+        <v>17.21684307909798</v>
       </c>
       <c r="O12" t="n">
-        <v>4.149569877140268</v>
+        <v>4.149318387289409</v>
       </c>
       <c r="P12" t="n">
-        <v>315.9099034412486</v>
+        <v>315.926635213002</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30123,28 +30181,28 @@
         <v>0.0591</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2079035581349168</v>
+        <v>-0.2096340510923219</v>
       </c>
       <c r="J13" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K13" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1163958424093346</v>
+        <v>0.1183697581092567</v>
       </c>
       <c r="M13" t="n">
-        <v>3.407026723651076</v>
+        <v>3.408754901884004</v>
       </c>
       <c r="N13" t="n">
-        <v>18.81211161135108</v>
+        <v>18.8113719660207</v>
       </c>
       <c r="O13" t="n">
-        <v>4.337293120294163</v>
+        <v>4.337207853679681</v>
       </c>
       <c r="P13" t="n">
-        <v>318.8812059729811</v>
+        <v>318.8990590661002</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30182,7 +30240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N484"/>
+  <dimension ref="A1:N485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65025,6 +65083,78 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>-46.384303659238896,168.02899839170163</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>-46.38408067240046,168.02815785430653</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>-46.383926725650134,168.0272880057526</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>-46.38376303881269,168.0264222926034</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>-46.383610987557766,168.02555163920937</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>-46.38344281807713,168.02468782955808</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>-46.38328602556513,168.02381918932556</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>-46.38311811403091,168.02295527048514</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>-46.38299472867181,168.02204600819553</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>-46.382937728321565,168.02112522358658</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>-46.38285761120561,168.0202293326998</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>-46.38287225257886,168.019329520456</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0535/nzd0535.xlsx
+++ b/data/nzd0535/nzd0535.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N485"/>
+  <dimension ref="A1:N486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23726,6 +23726,54 @@
         <v>309.03</v>
       </c>
       <c r="N485" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>333.11</v>
+      </c>
+      <c r="C486" t="n">
+        <v>324.65</v>
+      </c>
+      <c r="D486" t="n">
+        <v>324.86</v>
+      </c>
+      <c r="E486" t="n">
+        <v>322.92</v>
+      </c>
+      <c r="F486" t="n">
+        <v>322.14</v>
+      </c>
+      <c r="G486" t="n">
+        <v>320</v>
+      </c>
+      <c r="H486" t="n">
+        <v>318.96</v>
+      </c>
+      <c r="I486" t="n">
+        <v>317.79</v>
+      </c>
+      <c r="J486" t="n">
+        <v>320.78</v>
+      </c>
+      <c r="K486" t="n">
+        <v>316.26</v>
+      </c>
+      <c r="L486" t="n">
+        <v>307.99</v>
+      </c>
+      <c r="M486" t="n">
+        <v>310.32</v>
+      </c>
+      <c r="N486" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23742,7 +23790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B541"/>
+  <dimension ref="A1:B542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29155,6 +29203,16 @@
       </c>
       <c r="B541" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -29323,28 +29381,28 @@
         <v>0.1816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1772990706832872</v>
+        <v>0.1792168664813887</v>
       </c>
       <c r="J2" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K2" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06496886306257688</v>
+        <v>0.06645504618737241</v>
       </c>
       <c r="M2" t="n">
-        <v>3.651744287993321</v>
+        <v>3.655535657572156</v>
       </c>
       <c r="N2" t="n">
-        <v>26.00068699585749</v>
+        <v>25.9940582403605</v>
       </c>
       <c r="O2" t="n">
-        <v>5.099086878634006</v>
+        <v>5.09843684283335</v>
       </c>
       <c r="P2" t="n">
-        <v>323.5924351684887</v>
+        <v>323.5726111590077</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29401,28 +29459,28 @@
         <v>0.127</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3322108580866206</v>
+        <v>0.3343113836001922</v>
       </c>
       <c r="J3" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K3" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2361560545626723</v>
+        <v>0.2387556404926979</v>
       </c>
       <c r="M3" t="n">
-        <v>3.265091048998805</v>
+        <v>3.268960124405522</v>
       </c>
       <c r="N3" t="n">
-        <v>20.51560365096359</v>
+        <v>20.52966364773542</v>
       </c>
       <c r="O3" t="n">
-        <v>4.529415376289041</v>
+        <v>4.530967186786439</v>
       </c>
       <c r="P3" t="n">
-        <v>310.5418678450165</v>
+        <v>310.5201549818757</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29479,28 +29537,28 @@
         <v>0.0954</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2408054205804444</v>
+        <v>0.2432097569551289</v>
       </c>
       <c r="J4" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K4" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1832068010077328</v>
+        <v>0.1861280567323136</v>
       </c>
       <c r="M4" t="n">
-        <v>2.887937991510613</v>
+        <v>2.893668475621506</v>
       </c>
       <c r="N4" t="n">
-        <v>14.85778730939484</v>
+        <v>14.90099532329918</v>
       </c>
       <c r="O4" t="n">
-        <v>3.854580043194698</v>
+        <v>3.860180737128662</v>
       </c>
       <c r="P4" t="n">
-        <v>312.4334182905965</v>
+        <v>312.4085649735048</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29557,28 +29615,28 @@
         <v>0.1367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2570148987749143</v>
+        <v>0.258798454592056</v>
       </c>
       <c r="J5" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K5" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L5" t="n">
-        <v>0.189794035212921</v>
+        <v>0.1922389297342294</v>
       </c>
       <c r="M5" t="n">
-        <v>2.889426303845489</v>
+        <v>2.892875615574337</v>
       </c>
       <c r="N5" t="n">
-        <v>16.20617684938679</v>
+        <v>16.21339610030091</v>
       </c>
       <c r="O5" t="n">
-        <v>4.025689611654975</v>
+        <v>4.026586159552644</v>
       </c>
       <c r="P5" t="n">
-        <v>311.6062500413706</v>
+        <v>311.5878136533756</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29635,28 +29693,28 @@
         <v>0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.197493167324552</v>
+        <v>0.1984457023622577</v>
       </c>
       <c r="J6" t="n">
+        <v>485</v>
+      </c>
+      <c r="K6" t="n">
         <v>484</v>
       </c>
-      <c r="K6" t="n">
-        <v>483</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1721510035936233</v>
+        <v>0.1740176669580583</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4914514347894</v>
+        <v>2.490929473526136</v>
       </c>
       <c r="N6" t="n">
-        <v>10.79899602540532</v>
+        <v>10.78830336824258</v>
       </c>
       <c r="O6" t="n">
-        <v>3.286182591610716</v>
+        <v>3.284555277087383</v>
       </c>
       <c r="P6" t="n">
-        <v>314.4966516820999</v>
+        <v>314.4868114459498</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29713,28 +29771,28 @@
         <v>0.1233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1318728547354939</v>
+        <v>0.1315436398879665</v>
       </c>
       <c r="J7" t="n">
+        <v>485</v>
+      </c>
+      <c r="K7" t="n">
         <v>484</v>
       </c>
-      <c r="K7" t="n">
-        <v>483</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1000069187791776</v>
+        <v>0.09994782154559756</v>
       </c>
       <c r="M7" t="n">
-        <v>2.269702295279082</v>
+        <v>2.266734346131735</v>
       </c>
       <c r="N7" t="n">
-        <v>9.01068075611972</v>
+        <v>8.993451609034144</v>
       </c>
       <c r="O7" t="n">
-        <v>3.001779598191666</v>
+        <v>2.998908402908322</v>
       </c>
       <c r="P7" t="n">
-        <v>317.3055292354776</v>
+        <v>317.3089302146707</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29791,28 +29849,28 @@
         <v>0.106</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0007676352572946861</v>
+        <v>-0.0006465026845716211</v>
       </c>
       <c r="J8" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K8" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L8" t="n">
-        <v>3.162095290609734e-06</v>
+        <v>2.252957014503565e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.528611306967457</v>
+        <v>2.523950468560264</v>
       </c>
       <c r="N8" t="n">
-        <v>10.70987984916374</v>
+        <v>10.68798505243835</v>
       </c>
       <c r="O8" t="n">
-        <v>3.27259527732406</v>
+        <v>3.269248392587866</v>
       </c>
       <c r="P8" t="n">
-        <v>318.67343799863</v>
+        <v>318.6721858667437</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29869,28 +29927,28 @@
         <v>0.1023</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08360372775280638</v>
+        <v>-0.08430217117317244</v>
       </c>
       <c r="J9" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K9" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03703862810548619</v>
+        <v>0.03777827916102816</v>
       </c>
       <c r="M9" t="n">
-        <v>2.630555161298583</v>
+        <v>2.628434990409532</v>
       </c>
       <c r="N9" t="n">
-        <v>10.44374734563049</v>
+        <v>10.42844515290645</v>
       </c>
       <c r="O9" t="n">
-        <v>3.231678719432129</v>
+        <v>3.229310321555743</v>
       </c>
       <c r="P9" t="n">
-        <v>321.7660955009873</v>
+        <v>321.7733152211478</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29947,28 +30005,28 @@
         <v>0.1526</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09075959015939136</v>
+        <v>-0.0912843271378241</v>
       </c>
       <c r="J10" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K10" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03385166962370278</v>
+        <v>0.03437121908311835</v>
       </c>
       <c r="M10" t="n">
-        <v>2.860715003840617</v>
+        <v>2.857374878805633</v>
       </c>
       <c r="N10" t="n">
-        <v>13.51138484902885</v>
+        <v>13.48704354754169</v>
       </c>
       <c r="O10" t="n">
-        <v>3.675783569394265</v>
+        <v>3.67247104107598</v>
       </c>
       <c r="P10" t="n">
-        <v>324.5113781248492</v>
+        <v>324.5168022637725</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30025,28 +30083,28 @@
         <v>0.1109</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1495367867602204</v>
+        <v>-0.151089709442245</v>
       </c>
       <c r="J11" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K11" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09656492015055507</v>
+        <v>0.09855448085147145</v>
       </c>
       <c r="M11" t="n">
-        <v>2.770270711628162</v>
+        <v>2.77181921830468</v>
       </c>
       <c r="N11" t="n">
-        <v>12.02332955191757</v>
+        <v>12.02934383683798</v>
       </c>
       <c r="O11" t="n">
-        <v>3.467467310865031</v>
+        <v>3.468334447085226</v>
       </c>
       <c r="P11" t="n">
-        <v>324.1277545738838</v>
+        <v>324.1438069367069</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30103,28 +30161,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1931172809248725</v>
+        <v>-0.1942329929231067</v>
       </c>
       <c r="J12" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K12" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1107091863621846</v>
+        <v>0.1122042338649799</v>
       </c>
       <c r="M12" t="n">
-        <v>3.323460400010269</v>
+        <v>3.322501296271305</v>
       </c>
       <c r="N12" t="n">
-        <v>17.21684307909798</v>
+        <v>17.19724530373493</v>
       </c>
       <c r="O12" t="n">
-        <v>4.149318387289409</v>
+        <v>4.146956149241866</v>
       </c>
       <c r="P12" t="n">
-        <v>315.926635213002</v>
+        <v>315.9381681849966</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30181,28 +30239,28 @@
         <v>0.0591</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2096340510923219</v>
+        <v>-0.2108291336083427</v>
       </c>
       <c r="J13" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K13" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1183697581092567</v>
+        <v>0.1199333394065518</v>
       </c>
       <c r="M13" t="n">
-        <v>3.408754901884004</v>
+        <v>3.407817251122332</v>
       </c>
       <c r="N13" t="n">
-        <v>18.8113719660207</v>
+        <v>18.79082931307645</v>
       </c>
       <c r="O13" t="n">
-        <v>4.337207853679681</v>
+        <v>4.334839018127023</v>
       </c>
       <c r="P13" t="n">
-        <v>318.8990590661002</v>
+        <v>318.9114124809693</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30240,7 +30298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N485"/>
+  <dimension ref="A1:N486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65155,6 +65213,78 @@
         </is>
       </c>
     </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>-46.38430624502388,168.02899729390026</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>-46.38408455106775,168.0281562075732</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>-46.383937585888226,168.0272833947985</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>-46.383772088986134,168.02641845005988</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>-46.38361659003049,168.02554926044027</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>-46.383449368642594,168.02468504816923</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>-46.38329162800689,168.0238168104548</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>-46.38313276653039,168.02294904869044</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>-46.38300798607125,168.0220425204903</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>-46.38294830776158,168.02112425665337</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>-46.38286855616098,168.02022850549258</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>-46.38288382551119,168.01932864565543</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0535/nzd0535.xlsx
+++ b/data/nzd0535/nzd0535.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N486"/>
+  <dimension ref="A1:N489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23776,6 +23776,150 @@
       <c r="N486" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="C487" t="n">
+        <v>323.15</v>
+      </c>
+      <c r="D487" t="n">
+        <v>323.13</v>
+      </c>
+      <c r="E487" t="n">
+        <v>321.49</v>
+      </c>
+      <c r="F487" t="n">
+        <v>320.64</v>
+      </c>
+      <c r="G487" t="n">
+        <v>318.62</v>
+      </c>
+      <c r="H487" t="n">
+        <v>318.42</v>
+      </c>
+      <c r="I487" t="n">
+        <v>317.1</v>
+      </c>
+      <c r="J487" t="n">
+        <v>320.14</v>
+      </c>
+      <c r="K487" t="n">
+        <v>316.35</v>
+      </c>
+      <c r="L487" t="n">
+        <v>307.16</v>
+      </c>
+      <c r="M487" t="n">
+        <v>309.97</v>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>331.61</v>
+      </c>
+      <c r="C488" t="n">
+        <v>323.62</v>
+      </c>
+      <c r="D488" t="n">
+        <v>323.64</v>
+      </c>
+      <c r="E488" t="n">
+        <v>321.55</v>
+      </c>
+      <c r="F488" t="n">
+        <v>321.33</v>
+      </c>
+      <c r="G488" t="n">
+        <v>319.3</v>
+      </c>
+      <c r="H488" t="n">
+        <v>319.26</v>
+      </c>
+      <c r="I488" t="n">
+        <v>318.32</v>
+      </c>
+      <c r="J488" t="n">
+        <v>320.98</v>
+      </c>
+      <c r="K488" t="n">
+        <v>317.83</v>
+      </c>
+      <c r="L488" t="n">
+        <v>308.58</v>
+      </c>
+      <c r="M488" t="n">
+        <v>311.45</v>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>330.91</v>
+      </c>
+      <c r="C489" t="n">
+        <v>322.7</v>
+      </c>
+      <c r="D489" t="n">
+        <v>323.28</v>
+      </c>
+      <c r="E489" t="n">
+        <v>320.4</v>
+      </c>
+      <c r="F489" t="n">
+        <v>320.68</v>
+      </c>
+      <c r="G489" t="n">
+        <v>318.55</v>
+      </c>
+      <c r="H489" t="n">
+        <v>319.05</v>
+      </c>
+      <c r="I489" t="n">
+        <v>318.44</v>
+      </c>
+      <c r="J489" t="n">
+        <v>320.77</v>
+      </c>
+      <c r="K489" t="n">
+        <v>318.45</v>
+      </c>
+      <c r="L489" t="n">
+        <v>308.19</v>
+      </c>
+      <c r="M489" t="n">
+        <v>310.78</v>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23790,7 +23934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B542"/>
+  <dimension ref="A1:B545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29213,6 +29357,36 @@
       </c>
       <c r="B542" t="n">
         <v>0.12</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -29381,28 +29555,28 @@
         <v>0.1816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1792168664813887</v>
+        <v>0.1827474163472802</v>
       </c>
       <c r="J2" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K2" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06645504618737241</v>
+        <v>0.06966228452057777</v>
       </c>
       <c r="M2" t="n">
-        <v>3.655535657572156</v>
+        <v>3.653617145128026</v>
       </c>
       <c r="N2" t="n">
-        <v>25.9940582403605</v>
+        <v>25.8876220849211</v>
       </c>
       <c r="O2" t="n">
-        <v>5.09843684283335</v>
+        <v>5.087988019337418</v>
       </c>
       <c r="P2" t="n">
-        <v>323.5726111590077</v>
+        <v>323.5358824587431</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29459,28 +29633,28 @@
         <v>0.127</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3343113836001922</v>
+        <v>0.3386884429623939</v>
       </c>
       <c r="J3" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K3" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2387556404926979</v>
+        <v>0.2452911800261681</v>
       </c>
       <c r="M3" t="n">
-        <v>3.268960124405522</v>
+        <v>3.270960015877074</v>
       </c>
       <c r="N3" t="n">
-        <v>20.52966364773542</v>
+        <v>20.48542610519031</v>
       </c>
       <c r="O3" t="n">
-        <v>4.530967186786439</v>
+        <v>4.526082865479852</v>
       </c>
       <c r="P3" t="n">
-        <v>310.5201549818757</v>
+        <v>310.4746180774532</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29537,28 +29711,28 @@
         <v>0.0954</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2432097569551289</v>
+        <v>0.2484861534047916</v>
       </c>
       <c r="J4" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K4" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1861280567323136</v>
+        <v>0.193603526648474</v>
       </c>
       <c r="M4" t="n">
-        <v>2.893668475621506</v>
+        <v>2.901223029224334</v>
       </c>
       <c r="N4" t="n">
-        <v>14.90099532329918</v>
+        <v>14.92747993315676</v>
       </c>
       <c r="O4" t="n">
-        <v>3.860180737128662</v>
+        <v>3.863609702487657</v>
       </c>
       <c r="P4" t="n">
-        <v>312.4085649735048</v>
+        <v>312.3536680238867</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29615,28 +29789,28 @@
         <v>0.1367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.258798454592056</v>
+        <v>0.2619221753995762</v>
       </c>
       <c r="J5" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K5" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1922389297342294</v>
+        <v>0.1977242418566694</v>
       </c>
       <c r="M5" t="n">
-        <v>2.892875615574337</v>
+        <v>2.891499923698634</v>
       </c>
       <c r="N5" t="n">
-        <v>16.21339610030091</v>
+        <v>16.15678860786132</v>
       </c>
       <c r="O5" t="n">
-        <v>4.026586159552644</v>
+        <v>4.019550796775843</v>
       </c>
       <c r="P5" t="n">
-        <v>311.5878136533756</v>
+        <v>311.5553203644027</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29693,28 +29867,28 @@
         <v>0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1984457023622577</v>
+        <v>0.199729045238251</v>
       </c>
       <c r="J6" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K6" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1740176669580583</v>
+        <v>0.1777565883651478</v>
       </c>
       <c r="M6" t="n">
-        <v>2.490929473526136</v>
+        <v>2.481785271189922</v>
       </c>
       <c r="N6" t="n">
-        <v>10.78830336824258</v>
+        <v>10.72944731450629</v>
       </c>
       <c r="O6" t="n">
-        <v>3.284555277087383</v>
+        <v>3.27558350748478</v>
       </c>
       <c r="P6" t="n">
-        <v>314.4868114459498</v>
+        <v>314.4734665034811</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29771,28 +29945,28 @@
         <v>0.1233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1315436398879665</v>
+        <v>0.1291416554212766</v>
       </c>
       <c r="J7" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K7" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09994782154559756</v>
+        <v>0.09762791472146881</v>
       </c>
       <c r="M7" t="n">
-        <v>2.266734346131735</v>
+        <v>2.265097789351814</v>
       </c>
       <c r="N7" t="n">
-        <v>8.993451609034144</v>
+        <v>8.963230004714489</v>
       </c>
       <c r="O7" t="n">
-        <v>2.998908402908322</v>
+        <v>2.99386539522312</v>
       </c>
       <c r="P7" t="n">
-        <v>317.3089302146707</v>
+        <v>317.3339055997376</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29849,28 +30023,28 @@
         <v>0.106</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0006465026845716211</v>
+        <v>-0.000338505453123907</v>
       </c>
       <c r="J8" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K8" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L8" t="n">
-        <v>2.252957014503565e-06</v>
+        <v>6.260541349778492e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>2.523950468560264</v>
+        <v>2.510777794817714</v>
       </c>
       <c r="N8" t="n">
-        <v>10.68798505243835</v>
+        <v>10.62345866762554</v>
       </c>
       <c r="O8" t="n">
-        <v>3.269248392587866</v>
+        <v>3.259364764432717</v>
       </c>
       <c r="P8" t="n">
-        <v>318.6721858667437</v>
+        <v>318.6689771939139</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29927,28 +30101,28 @@
         <v>0.1023</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08430217117317244</v>
+        <v>-0.08615623573996166</v>
       </c>
       <c r="J9" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K9" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03777827916102816</v>
+        <v>0.03984859721815848</v>
       </c>
       <c r="M9" t="n">
-        <v>2.628434990409532</v>
+        <v>2.620875112363192</v>
       </c>
       <c r="N9" t="n">
-        <v>10.42844515290645</v>
+        <v>10.38118352574391</v>
       </c>
       <c r="O9" t="n">
-        <v>3.229310321555743</v>
+        <v>3.221984408054128</v>
       </c>
       <c r="P9" t="n">
-        <v>321.7733152211478</v>
+        <v>321.7925963477877</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30005,28 +30179,28 @@
         <v>0.1526</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0912843271378241</v>
+        <v>-0.09300284865896755</v>
       </c>
       <c r="J10" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K10" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03437121908311835</v>
+        <v>0.03606753648114536</v>
       </c>
       <c r="M10" t="n">
-        <v>2.857374878805633</v>
+        <v>2.84810215679583</v>
       </c>
       <c r="N10" t="n">
-        <v>13.48704354754169</v>
+        <v>13.41743138962764</v>
       </c>
       <c r="O10" t="n">
-        <v>3.67247104107598</v>
+        <v>3.662981216117227</v>
       </c>
       <c r="P10" t="n">
-        <v>324.5168022637725</v>
+        <v>324.534677487959</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30083,28 +30257,28 @@
         <v>0.1109</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.151089709442245</v>
+        <v>-0.1541287318136052</v>
       </c>
       <c r="J11" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K11" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09855448085147145</v>
+        <v>0.1030663017759267</v>
       </c>
       <c r="M11" t="n">
-        <v>2.77181921830468</v>
+        <v>2.768937134335925</v>
       </c>
       <c r="N11" t="n">
-        <v>12.02934383683798</v>
+        <v>11.99934698313245</v>
       </c>
       <c r="O11" t="n">
-        <v>3.468334447085226</v>
+        <v>3.464007358989361</v>
       </c>
       <c r="P11" t="n">
-        <v>324.1438069367069</v>
+        <v>324.1754119597716</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30161,28 +30335,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1942329929231067</v>
+        <v>-0.1975164799980482</v>
       </c>
       <c r="J12" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K12" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1122042338649799</v>
+        <v>0.1166986679667593</v>
       </c>
       <c r="M12" t="n">
-        <v>3.322501296271305</v>
+        <v>3.319351542465949</v>
       </c>
       <c r="N12" t="n">
-        <v>17.19724530373493</v>
+        <v>17.13943159149374</v>
       </c>
       <c r="O12" t="n">
-        <v>4.146956149241866</v>
+        <v>4.139979660758461</v>
       </c>
       <c r="P12" t="n">
-        <v>315.9381681849966</v>
+        <v>315.9723224918569</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30239,28 +30413,28 @@
         <v>0.0591</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2108291336083427</v>
+        <v>-0.213839016912902</v>
       </c>
       <c r="J13" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K13" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1199333394065518</v>
+        <v>0.1241978550171621</v>
       </c>
       <c r="M13" t="n">
-        <v>3.407817251122332</v>
+        <v>3.401981788936348</v>
       </c>
       <c r="N13" t="n">
-        <v>18.79082931307645</v>
+        <v>18.71597952572145</v>
       </c>
       <c r="O13" t="n">
-        <v>4.334839018127023</v>
+        <v>4.326196889384653</v>
       </c>
       <c r="P13" t="n">
-        <v>318.9114124809693</v>
+        <v>318.9427213420261</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30298,7 +30472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N486"/>
+  <dimension ref="A1:N489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65285,6 +65459,222 @@
         </is>
       </c>
     </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>-46.38429236797762,168.02900318543294</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>-46.38407162217665,168.0281616966833</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>-46.38392267460887,168.02728972571114</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-46.383759763511776,168.02642368323785</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>-46.38360366124718,168.0255547499066</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>-46.38343747419471,168.02469009858532</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>-46.38328697367067,168.02381878674746</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>-46.38312681933947,168.02295157400755</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>-46.38300232958083,168.0220440085781</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>-46.38294911466802,168.02112418290417</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>-46.38286111000282,168.02022906826477</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>-46.38288068556832,168.0193288830045</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>-46.38429331609882,168.029002782906</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>-46.384075673229226,168.02815997676242</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>-46.383927070419595,168.02728785937313</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-46.38376028066455,168.02642346366403</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>-46.38360960848755,168.02555222475246</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>-46.383443335227035,168.0246876099748</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>-46.383294213749195,168.02381571251428</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>-46.38313733466248,168.02294710895367</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>-46.38300975372448,168.02204205546275</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>-46.38296238379612,168.02112297013966</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>-46.382873849213155,168.02022810544958</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>-46.38289396304103,168.01932787935684</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>-46.38428728260032,168.029005344441</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-46.384067743509235,168.02816334341574</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>-46.38392396749438,168.02728917678823</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-46.38375036856956,168.02642767216201</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>-46.38360400601474,168.02555460352087</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>-46.38343687085314,168.0246903547658</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>-46.38329240372958,168.02381648107263</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>-46.38313836895652,168.02294666976795</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>-46.383007897688586,168.02204254374163</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>-46.38296794248491,168.0211224620894</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>-46.38287035041596,168.02022836988482</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>-46.38288795229325,168.01932833371094</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
